--- a/www/download/IND.value.m.mv.zdW16.xlsx
+++ b/www/download/IND.value.m.mv.zdW16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.777</t>
+          <t>1497824.56925551</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.802</t>
+          <t>1529692.19923308</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.742</t>
+          <t>1467598.55119559</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1137095.59578256</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.225</t>
+          <t>1004778.10781679</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1.142</t>
+          <t>918874.524039087</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>899480.230454311</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>799990.486821367</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.963</t>
+          <t>769323.05754246</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.039</t>
+          <t>827554.098076391</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>679907.78357846</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>658165.853152577</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>632365.342130211</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>654275.951593205</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>684807.143811702</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.799</t>
+          <t>1365444.97034723</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1322239.92613515</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1138947.30131718</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>974850.936532989</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.139</t>
+          <t>840521.735887508</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1.043</t>
+          <t>773895.973624776</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.988</t>
+          <t>739357.903712263</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>637166.326544658</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.751</t>
+          <t>566049.112182107</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>630833.551868485</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.891</t>
+          <t>673547.359676139</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.841</t>
+          <t>639926.592137721</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.872</t>
+          <t>668157.241508101</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>682818.774493411</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.632</t>
+          <t>631712.226486602</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>1049855.83044103</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.291</t>
+          <t>1035844.57999759</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.206</t>
+          <t>964008.817250208</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.071</t>
+          <t>850097.493529136</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.002</t>
+          <t>795349.987492812</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.942</t>
+          <t>733621.509894001</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>713752.368229655</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.822</t>
+          <t>646128.643286883</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>605646.068216719</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>669145.717943859</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.914</t>
+          <t>728412.398918248</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.903</t>
+          <t>721250.056612785</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.891</t>
+          <t>711395.891708663</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>688961.946799259</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.732</t>
+          <t>732066.143485683</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>11.436</t>
+          <t>10317257.3260675</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>9194190.74198995</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8.712</t>
+          <t>7846138.40839663</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6.797</t>
+          <t>6108148.52893448</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5.484</t>
+          <t>4969279.62304962</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.732</t>
+          <t>4225145.25210784</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.292</t>
+          <t>3803557.65900152</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>3.482</t>
+          <t>3081719.9661739</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3.018</t>
+          <t>2687207.78236378</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3.192</t>
+          <t>2778981.49312691</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>3.029</t>
+          <t>2669838.2313646</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2.607</t>
+          <t>2292395.99569229</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2360930.65711827</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2.672</t>
+          <t>2332507.30822475</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2.385</t>
+          <t>2384759.63629006</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.382</t>
+          <t>6605294.68841741</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8.266</t>
+          <t>7341509.59455444</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8.787</t>
+          <t>7758862.12321887</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>7.949</t>
+          <t>6988214.76866022</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>6241805.34330438</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>5.814</t>
+          <t>5126298.73521813</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4.836</t>
+          <t>4273873.95723342</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3.833</t>
+          <t>3401129.46080701</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.199</t>
+          <t>2813894.16105437</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3.369</t>
+          <t>2914734.60543168</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2.549</t>
+          <t>2187624.37738038</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2.168</t>
+          <t>1859749.6804713</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2.268</t>
+          <t>1929404.55301748</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2.296</t>
+          <t>1955422.08690971</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1.987</t>
+          <t>1987480.83891765</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1153545.24273642</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>1177015.70442506</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>1158511.63397232</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.212</t>
+          <t>1075177.58559368</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.102</t>
+          <t>973772.90830585</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.981</t>
+          <t>856916.678048687</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.893</t>
+          <t>775462.281533244</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.784</t>
+          <t>680001.935903028</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>634962.142359514</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.795</t>
+          <t>681263.206843319</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>621034.084195745</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>597582.091283729</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>583272.508246556</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>570058.711859715</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.597</t>
+          <t>596565.329265069</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23.021</t>
+          <t>20488158.5169542</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20.843</t>
+          <t>18739149.2076749</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>19.461</t>
+          <t>17608725.1516522</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>17.711</t>
+          <t>16070284.7033303</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>13914682.2470571</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>13.357</t>
+          <t>12072433.854582</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>11.894</t>
+          <t>10779120.4405942</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>9.477</t>
+          <t>8632843.67772921</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>7.913</t>
+          <t>7106693.71162829</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>7.602</t>
+          <t>6730216.23710172</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>6.413</t>
+          <t>5716485.30517547</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>5.641</t>
+          <t>4986669.70009591</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>5.123</t>
+          <t>4480529.81994122</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>4.546</t>
+          <t>3963869.37072483</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3.617</t>
+          <t>3616790.87718501</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2446884.02306525</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.895</t>
+          <t>2514146.44452018</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.795</t>
+          <t>2400781.26217975</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2.567</t>
+          <t>2251782.98922303</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2.253</t>
+          <t>1996097.90969864</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2.048</t>
+          <t>1816486.93383955</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1.855</t>
+          <t>1630183.85006485</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1383212.53467574</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>1424481.42128317</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2.328</t>
+          <t>2088305.64159331</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1115711.8452016</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1.253</t>
+          <t>1059963.13247684</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1.386</t>
+          <t>1179065.91670998</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>1258310.29328646</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1329751.67036136</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.232</t>
+          <t>3578255.30414946</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.751</t>
+          <t>3130087.42363526</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.241</t>
+          <t>2657464.87699399</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.638</t>
+          <t>2166538.32814451</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1830985.82035721</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1.978</t>
+          <t>1650715.4253461</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1.723</t>
+          <t>1433314.83256357</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1.451</t>
+          <t>1204843.14590898</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>984933.494474741</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1118893.07277762</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1116226.03507181</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1.291</t>
+          <t>1036736.95649959</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1089266.00215848</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1.381</t>
+          <t>1125635.69881921</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1.118</t>
+          <t>1118199.24171718</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1166929.46137771</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1134830.56100238</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1067153.75293221</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.238</t>
+          <t>971237.936466916</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.105</t>
+          <t>869344.143040129</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>856168.520312878</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>783342.060204887</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>684494.121595367</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.795</t>
+          <t>618997.077976265</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.872</t>
+          <t>672403.291516057</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>667558.890419091</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>613197.991374627</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>0.784</t>
+          <t>614919.416997523</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>604897.893252394</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0.586</t>
+          <t>585754.632488211</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.339</t>
+          <t>1088578.41272101</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1073503.72100362</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>1010048.52524065</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.138</t>
+          <t>906032.791418863</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>857075.190833978</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>795086.908033578</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>695768.085449369</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.788</t>
+          <t>622724.152421127</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>566216.037076957</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>591097.528384783</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>572395.412330945</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>535318.74339886</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>534769.844256763</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>533841.547379334</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.527</t>
+          <t>527038.814869964</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.785</t>
+          <t>1555914.90544044</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.708</t>
+          <t>1492501.50824922</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1365478.54000816</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.276</t>
+          <t>1108434.39855136</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>973090.913758963</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1.052</t>
+          <t>905270.305189552</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1.006</t>
+          <t>864027.93926135</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>732694.447104656</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>679210.107876129</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>719395.529480921</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0.953</t>
+          <t>798324.226091993</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>777477.210853544</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0.976</t>
+          <t>806636.193307543</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0.936</t>
+          <t>771550.563909702</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>787324.981317022</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5.606</t>
+          <t>5133260.07299615</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5.271</t>
+          <t>4770016.01661283</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4.579</t>
+          <t>4107671.20813364</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3.824</t>
+          <t>3406367.72858758</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>3.149</t>
+          <t>2840549.23639929</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2364497.95801577</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2.452</t>
+          <t>2183477.79706426</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1.891</t>
+          <t>1681987.58582108</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1.728</t>
+          <t>1522820.68464039</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1567100.72323868</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.626</t>
+          <t>1421427.54006329</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1363837.83903596</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1354650.68982943</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1226322.28243188</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1.203</t>
+          <t>1202599.39172729</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1193827.78348729</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>1166685.58801836</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.347</t>
+          <t>1118382.82895447</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.202</t>
+          <t>984426.772826131</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.067</t>
+          <t>876220.931394247</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>850357.740622625</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.993</t>
+          <t>799987.168818175</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>683112.787198998</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>660143.880583797</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>614654.006351175</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>648303.531418055</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>575462.466056429</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>610254.466172643</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>598738.678355831</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>558610.790251811</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.252</t>
+          <t>1069704.83014154</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.211</t>
+          <t>1031641.7361173</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>967934.046123782</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.037</t>
+          <t>871605.922999755</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>818330.76928201</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>784153.903904649</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.874</t>
+          <t>731735.225017202</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>638030.764161356</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.699</t>
+          <t>583588.509543314</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>658927.03928635</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>636303.074086701</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>621198.33581925</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>627314.16763582</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.693</t>
+          <t>582516.19651939</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.582</t>
+          <t>582096.699323208</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.224</t>
+          <t>1031758.32286009</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.254</t>
+          <t>1059024.94707846</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.259</t>
+          <t>1066263.99280101</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.148</t>
+          <t>971349.006152142</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.953</t>
+          <t>800429.017792451</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>827350.342462022</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>757426.752695387</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>632906.554388063</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>622555.025212878</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>746753.658326124</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>698098.607755269</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>693131.520311903</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>682878.887770125</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>692537.120981167</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>602299.380051553</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.656</t>
+          <t>2368201.56539708</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2507574.14387572</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.419</t>
+          <t>2138735.56959649</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.864</t>
+          <t>1663686.54273159</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1419432.159698</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.632</t>
+          <t>1465952.41733426</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.439</t>
+          <t>1288199.79418024</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.278</t>
+          <t>1144536.93424817</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>913125.107044444</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1020568.35672101</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1009146.60617034</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1.119</t>
+          <t>989885.011896871</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1.174</t>
+          <t>1040543.46246833</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1.184</t>
+          <t>1042196.82212934</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1.061</t>
+          <t>1060935.6457726</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>4919868.31305119</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5.023</t>
+          <t>4230519.93554234</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>4.255</t>
+          <t>3584205.37725332</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.488</t>
+          <t>2923643.09159726</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2.783</t>
+          <t>2346879.0944226</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2.586</t>
+          <t>2195049.24108745</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2.494</t>
+          <t>2123168.4415681</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.063</t>
+          <t>1735971.82007096</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.739</t>
+          <t>1447498.96684744</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.099</t>
+          <t>1727323.57645181</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.882</t>
+          <t>1548482.88668589</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1.709</t>
+          <t>1429236.55237496</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1493615.86772129</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.681</t>
+          <t>1394406.91227111</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1449641.9596142</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>18.817</t>
+          <t>17396763.7463595</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>19.713</t>
+          <t>18423819.8905874</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>17.399</t>
+          <t>16266742.8714461</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>15.798</t>
+          <t>14707817.1211611</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>14.892</t>
+          <t>13857900.8634525</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>12.819</t>
+          <t>11969302.7970417</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>9.779</t>
+          <t>8805016.24620227</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>7509098.71729549</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>7.163</t>
+          <t>6402068.12307429</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>6.995</t>
+          <t>6200030.30324876</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>5.711</t>
+          <t>5061856.97582309</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>4.964</t>
+          <t>4389048.55612606</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>5.241</t>
+          <t>4629571.05047788</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>5.699</t>
+          <t>5089594.99015529</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>5.737</t>
+          <t>5736727.84606015</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>43.171</t>
+          <t>38659022.2169429</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>43.216</t>
+          <t>38959486.6805943</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>43.622</t>
+          <t>39777137.3398066</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>38.979</t>
+          <t>35472355.6654053</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>35.698</t>
+          <t>32793114.895922</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>30.736</t>
+          <t>28334965.3181259</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>26.775</t>
+          <t>24698276.0374931</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>21.153</t>
+          <t>19335362.4300968</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>17535465.0033955</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>18.999</t>
+          <t>17207323.2052627</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>15.26</t>
+          <t>13822055.2691951</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>13.725</t>
+          <t>12421366.7956707</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>15.953</t>
+          <t>14252980.4394104</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>17.152</t>
+          <t>15321698.5267926</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>15.921</t>
+          <t>15921262.5359048</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>1245167.33615578</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1300677.22207554</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1178135.91400159</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.087</t>
+          <t>949871.838146777</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.939</t>
+          <t>819706.403409702</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.961</t>
+          <t>836733.651503914</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>780724.273959988</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>667606.892255644</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.689</t>
+          <t>599304.089466499</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.908</t>
+          <t>738336.828262872</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>672432.087341549</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.813</t>
+          <t>627630.794770632</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0.916</t>
+          <t>711956.417032952</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>698227.636848398</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>0.702</t>
+          <t>701717.075607621</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>1226068.85213368</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1226127.3523972</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>1117242.50331748</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.138</t>
+          <t>944227.512505446</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.035</t>
+          <t>857291.37150633</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.989</t>
+          <t>812744.055071867</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>794410.711539813</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.835</t>
+          <t>685851.57820839</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>628340.133315866</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>682638.388010738</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>0.891</t>
+          <t>713324.536688008</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>698258.772252702</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>707646.728528734</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>670702.340598792</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>675965.029208345</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1255887.07252295</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.741</t>
+          <t>1351039.81585876</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1353542.70107088</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.734</t>
+          <t>1317440.86306657</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.621</t>
+          <t>1239355.36341364</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1190032.17483216</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1213083.54436101</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1119630.75123822</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>974080.508075965</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.283</t>
+          <t>888068.359574525</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>820198.84539013</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>813903.957169885</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1.153</t>
+          <t>802843.702369444</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>940503.730784506</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1.005</t>
+          <t>1004984.93898559</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.243</t>
+          <t>2732196.66630055</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3.407</t>
+          <t>2866580.97541765</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3.213</t>
+          <t>2685394.66535547</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3.025</t>
+          <t>2531016.31051657</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2.792</t>
+          <t>2323611.41356962</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2.301</t>
+          <t>1879394.69783693</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2.139</t>
+          <t>1753105.4754284</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1.838</t>
+          <t>1517781.02184487</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1.938</t>
+          <t>1603394.38875406</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2.115</t>
+          <t>1740201.6667907</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.765</t>
+          <t>1459094.50428476</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1.747</t>
+          <t>1418261.96638657</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1.719</t>
+          <t>1389850.40833523</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1.715</t>
+          <t>1393702.92010232</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>1.299</t>
+          <t>1299377.62114307</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7.732</t>
+          <t>6786945.74215589</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>5975260.6647669</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>5.609</t>
+          <t>4971823.16724087</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4.535</t>
+          <t>4031698.47003262</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3.838</t>
+          <t>3454854.18790753</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3.386</t>
+          <t>3042339.2975141</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2.955</t>
+          <t>2640123.51897346</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2.225</t>
+          <t>1995996.17542976</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1.881</t>
+          <t>1684172.54594214</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2.145</t>
+          <t>1850564.49037313</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>1640048.84714171</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1.607</t>
+          <t>1413880.23595413</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1.709</t>
+          <t>1504112.35555343</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1.562</t>
+          <t>1365061.00315051</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1414623.60139624</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.063</t>
+          <t>862491.519424264</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.104</t>
+          <t>904493.846895382</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.966</t>
+          <t>796197.445497607</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>707254.757670572</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>610679.074491597</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>581197.733049103</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.716</t>
+          <t>559315.206556028</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>472832.176880958</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>593614.158118561</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.908</t>
+          <t>724926.304562997</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>760004.361140978</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>621895.822116274</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.903</t>
+          <t>721355.638560801</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>567302.863357561</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.563</t>
+          <t>562689.32607039</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7.172</t>
+          <t>6058664.04934072</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>5897463.94638535</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>6.087</t>
+          <t>5423811.04573334</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4.947</t>
+          <t>4408654.12426687</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>3.946</t>
+          <t>3532264.86603983</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>3.547</t>
+          <t>3154009.47591689</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>3.092</t>
+          <t>2724216.1635224</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2.255</t>
+          <t>1943494.21007044</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2.021</t>
+          <t>1735997.48591194</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2.173</t>
+          <t>1829258.35407124</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2.015</t>
+          <t>1702667.85580115</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1.865</t>
+          <t>1539379.70527571</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1.978</t>
+          <t>1640970.08658442</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1.807</t>
+          <t>1508382.05120459</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1.503</t>
+          <t>1502982.47079075</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.188</t>
+          <t>2809792.94410507</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.007</t>
+          <t>2615339.90314743</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2.985</t>
+          <t>2575456.43110867</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>3.115</t>
+          <t>2711312.5049798</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>3.005</t>
+          <t>2632020.8045134</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2374508.93993191</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2.563</t>
+          <t>2237630.14031487</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2.399</t>
+          <t>2103581.16877015</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2.282</t>
+          <t>1988789.69185835</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2.705</t>
+          <t>2345704.3933</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2.398</t>
+          <t>2093708.93252017</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2.231</t>
+          <t>1944005.94436108</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2.238</t>
+          <t>1961224.35117893</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2.117</t>
+          <t>1846627.46909574</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1.861</t>
+          <t>1860937.26405737</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2.517</t>
+          <t>2245911.41700694</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2197833.97375717</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2.212</t>
+          <t>1988630.54688953</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2.315</t>
+          <t>2081123.71097713</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1.734</t>
+          <t>1535827.33288054</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1.692</t>
+          <t>1500208.56646366</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1417694.49512555</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1294726.82350777</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1360298.2987284</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1188435.89921456</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1.472</t>
+          <t>1239307.58329221</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1116590.87251907</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>1429342.86003629</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1135327.58630516</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>1.056</t>
+          <t>1055864.96301491</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.351</t>
+          <t>1108387.64443238</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1137862.30261914</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.353</t>
+          <t>1120552.2259158</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.276</t>
+          <t>1052468.22924191</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.104</t>
+          <t>900314.672865196</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1.022</t>
+          <t>827939.382376348</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.977</t>
+          <t>791442.743191917</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>685039.813160014</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>649084.669893102</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.094</t>
+          <t>845290.522976751</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1.182</t>
+          <t>921362.964711978</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>863927.485050893</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1.092</t>
+          <t>847971.81729361</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>1.242</t>
+          <t>948413.892412323</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>0.931</t>
+          <t>930781.057279354</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.633</t>
+          <t>4269170.12597527</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4.247</t>
+          <t>3943389.57644933</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3664700.11026634</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3.589</t>
+          <t>3325843.18645675</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>3.063</t>
+          <t>2846316.49547904</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.718</t>
+          <t>2520646.78222716</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.469</t>
+          <t>2284532.82379273</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.042</t>
+          <t>1885293.46472834</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.756</t>
+          <t>1615224.6261141</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.161</t>
+          <t>1987291.44550039</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.983</t>
+          <t>1810870.8982055</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1599387.96922365</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.858</t>
+          <t>1697437.26212299</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.805</t>
+          <t>1646931.04997783</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1608076.73305318</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2.962</t>
+          <t>2589993.10756368</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2.923</t>
+          <t>2559871.92149019</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2.656</t>
+          <t>2311833.7220219</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2.233</t>
+          <t>1933531.04857237</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2.061</t>
+          <t>1789628.07664198</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1.893</t>
+          <t>1635517.89585989</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>1.822</t>
+          <t>1561173.16885175</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1353509.29780559</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>1.443</t>
+          <t>1225712.03753756</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1.482</t>
+          <t>1246319.71981347</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1210795.82462898</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1182063.42518557</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>1218331.48909425</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>1182054.5445134</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>1.203</t>
+          <t>1202553.50430625</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>15.088</t>
+          <t>13197123.5163268</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>11647926.9985585</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>11.154</t>
+          <t>9880678.13620433</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>8.682</t>
+          <t>7690978.92778523</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>6.595</t>
+          <t>5945284.01963916</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>5.387</t>
+          <t>4821077.85845136</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>4.283</t>
+          <t>3842184.89398838</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>3.336</t>
+          <t>2956068.31256262</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2.678</t>
+          <t>2369650.11704962</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2.964</t>
+          <t>2591247.37973239</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2.664</t>
+          <t>2362771.24623647</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2.436</t>
+          <t>2163071.14412095</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2.319</t>
+          <t>2052412.80753937</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2.048</t>
+          <t>1811126.66554525</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>1.825</t>
+          <t>1824877.54670685</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>11.586</t>
+          <t>10502859.7812067</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>9.544</t>
+          <t>8663095.31231035</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>8.485</t>
+          <t>7624483.88731947</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>7.283</t>
+          <t>6509282.54067897</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>5.278</t>
+          <t>4891120.18714511</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>4.406</t>
+          <t>3981727.9780651</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>3.465</t>
+          <t>3134446.59438965</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2.617</t>
+          <t>2403818.62164363</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1.932</t>
+          <t>1753017.43411145</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2.451</t>
+          <t>2215890.72179291</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2.122</t>
+          <t>1915867.55709355</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1.724</t>
+          <t>1546753.46918945</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1.721</t>
+          <t>1539951.04359295</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1.581</t>
+          <t>1404730.68965592</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>1.427</t>
+          <t>1427057.76645864</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>5.571</t>
+          <t>4631541.72877018</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5.227</t>
+          <t>4241754.62795967</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4.409</t>
+          <t>3602392.51507344</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>3.231</t>
+          <t>2680666.95858584</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2.701</t>
+          <t>2283509.75201261</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2.486</t>
+          <t>2076442.67742909</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2.215</t>
+          <t>1844261.2662586</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1.717</t>
+          <t>1434533.85424409</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1159596.84552338</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1.634</t>
+          <t>1346364.04962358</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1259219.7512723</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1.439</t>
+          <t>1165627.211478</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1.471</t>
+          <t>1215584.51962176</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>1165312.56598693</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>1.121</t>
+          <t>1121010.13780115</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2.712</t>
+          <t>2349332.93009213</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2.695</t>
+          <t>2332408.27814959</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2.485</t>
+          <t>2160480.66297575</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1813006.28494678</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1643717.71647332</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1.766</t>
+          <t>1512320.70296175</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1.641</t>
+          <t>1398519.59000482</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1.349</t>
+          <t>1155999.21832884</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1.211</t>
+          <t>1033482.75357552</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1129577.07342247</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1131918.71695041</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1.274</t>
+          <t>1078176.02506245</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1.341</t>
+          <t>1129000.58005833</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1055884.50344351</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>1024832.51230726</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.233</t>
+          <t>987950.286684156</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>993295.303551362</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>1.141</t>
+          <t>908692.399083692</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>766555.365710549</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>706841.643821006</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.885</t>
+          <t>686813.075614697</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>625154.552565594</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>533356.325783237</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>497154.544407166</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>577111.489769061</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>531696.347363435</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>492335.613626545</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>494311.95574091</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>486876.251663723</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>492300.63688232</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4.683</t>
+          <t>4053090.03163671</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6.246</t>
+          <t>5519159.17803186</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>4693232.48822666</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>4.111</t>
+          <t>3607315.94492804</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>3.487</t>
+          <t>3036554.82007849</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2.909</t>
+          <t>2499722.97833271</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2.684</t>
+          <t>2285835.4354376</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2.193</t>
+          <t>1867481.74189518</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1.967</t>
+          <t>1644268.80261919</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2.277</t>
+          <t>1853076.90019427</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2.044</t>
+          <t>1701831.41578422</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2.042</t>
+          <t>1703674.69814744</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2.113</t>
+          <t>1772426.03519872</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2.198</t>
+          <t>1849598.38513314</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2.083</t>
+          <t>2082930.5465791</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>5.157</t>
+          <t>4526957.03960649</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5.338</t>
+          <t>4658999.77848312</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>5.377</t>
+          <t>4671003.6332242</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>5.392</t>
+          <t>4683213.37893568</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>5.039</t>
+          <t>4366297.89328639</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>4.604</t>
+          <t>3942325.72469155</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>4.374</t>
+          <t>3727554.34558179</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>4.119</t>
+          <t>3549106.62135144</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>3.911</t>
+          <t>3309200.90646031</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>3.959</t>
+          <t>3386497.20201467</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>3.567</t>
+          <t>3100298.0425067</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>3.251</t>
+          <t>2783028.1419102</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>2798213.91974234</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>3.199</t>
+          <t>2743520.84907233</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2.766</t>
+          <t>2765683.80044569</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.379</t>
+          <t>1166145.75597938</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1110614.05462719</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1124606.75348054</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1.274</t>
+          <t>1067486.49415398</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1.234</t>
+          <t>1033005.92103036</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1.169</t>
+          <t>970946.976903646</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1.102</t>
+          <t>911011.152191785</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>799278.399666224</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>754662.680201411</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>727961.432532037</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>0.842</t>
+          <t>679653.273648092</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>679541.257237775</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>642815.361836739</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>629688.542830263</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>0.616</t>
+          <t>616200.476052389</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>16.802</t>
+          <t>14972132.516924</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>17.253</t>
+          <t>15477719.8205301</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>17.727</t>
+          <t>15791885.5921226</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>17.017</t>
+          <t>15198666.88005</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>15.561</t>
+          <t>13994100.1784614</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>12458893.5991703</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>12.459</t>
+          <t>11081536.5182674</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>10.449</t>
+          <t>9422388.14454857</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>9.195</t>
+          <t>8290850.75468359</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>9.727</t>
+          <t>8743927.59199108</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>8.471</t>
+          <t>7638077.47939947</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>7.785</t>
+          <t>7026063.08874169</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>7.818</t>
+          <t>7086808.73918143</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>7054641.18901324</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>7.123</t>
+          <t>7122676.32077627</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>250.12</t>
+          <t>220719548.477038</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>242.348</t>
+          <t>214680318.739691</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>226.143</t>
+          <t>200608237.551603</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>198.788</t>
+          <t>176210043.771444</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>174.253</t>
+          <t>155372931.440588</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>153.973</t>
+          <t>136548266.416577</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>135.843</t>
+          <t>119724581.355705</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>111.925</t>
+          <t>98534669.9000515</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>99.572</t>
+          <t>87104996.3270093</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>105.742</t>
+          <t>91366353.2841843</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>92.824</t>
+          <t>80312586.6463024</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>85.032</t>
+          <t>73169040.1825951</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>88.678</t>
+          <t>76192981.6227776</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>88.083</t>
+          <t>75765000.2628981</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>76.963</t>
+          <t>76962959.1761534</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>4802556.82938423</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4.432</t>
+          <t>4091763.56752683</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3.919</t>
+          <t>3595303.53653279</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>3.149</t>
+          <t>2887797.39424343</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2.646</t>
+          <t>2415958.40585681</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2.509</t>
+          <t>2296303.76737035</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2.205</t>
+          <t>1998674.19862146</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>1.817</t>
+          <t>1644012.37189828</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>1.632</t>
+          <t>1462871.81501225</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>1.743</t>
+          <t>1537691.67872614</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1619999.12185492</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1538921.34237398</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1.843</t>
+          <t>1628904.00383574</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>1.886</t>
+          <t>1670671.04243668</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>1.699</t>
+          <t>1699314.89757593</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1298616.99204875</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1242517.54541876</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>1.351</t>
+          <t>1111497.92614114</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>985097.60654953</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1.019</t>
+          <t>846231.612390098</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1.024</t>
+          <t>847474.751927398</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>839347.432036565</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>737052.245509597</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>641931.155150088</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>0.781</t>
+          <t>631186.181551595</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>573113.362928485</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>552351.758117642</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>0.713</t>
+          <t>577736.243996628</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>566841.652720204</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>0.541</t>
+          <t>541210.66219947</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>954214.489052793</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1.123</t>
+          <t>891642.222435667</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>785867.364325922</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.906</t>
+          <t>716385.530813816</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>648798.328709281</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>576399.334244706</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.632</t>
+          <t>500074.039401775</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>438274.176466744</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>385416.410122252</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>393280.367351092</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>361582.649515035</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>338708.400980928</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>339250.877154915</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>332709.160157269</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>327884.502554152</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>value.m.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
